--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity2D\Unity2Dproject\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\promotion_task_3D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E749B1-511C-42B3-AC90-912C343CC576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE48054-6103-4380-B690-9D18673BA61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7176" yWindow="1572" windowWidth="12840" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7692" yWindow="1860" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,114 +20,137 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
-  <si>
-    <t>Item_Equip_Hat_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Corn</t>
-  </si>
-  <si>
-    <t>상자다. 딱히 의미가 있진 않다.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>옥수수다</t>
-  </si>
-  <si>
     <t>(name)</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Legend</t>
-  </si>
-  <si>
-    <t>의문의 모자</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>지역에 나타나는 금화</t>
-  </si>
-  <si>
     <t>ItemType</t>
   </si>
   <si>
-    <t>Item_DummyBox_1</t>
-  </si>
-  <si>
     <t>MaxStackCount</t>
   </si>
   <si>
-    <t>착용하면 공격력이 강해진다.</t>
-  </si>
-  <si>
     <t>캐릭터 전체 컨셉이나 스토리</t>
   </si>
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
   <si>
-    <t>Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Item_Corn_1</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
     <t>IconPath</t>
   </si>
   <si>
-    <t>상자</t>
-  </si>
-  <si>
-    <t>옥수수</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>화폐</t>
-  </si>
-  <si>
-    <t>Item_Potato_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Box_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Equip_Hat_1</t>
-  </si>
-  <si>
-    <t>감자</t>
-  </si>
-  <si>
-    <t>감자다. 딱히 의미가 있진 않다.</t>
-  </si>
-  <si>
     <t>SellingPrice</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PrefabPath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potion</t>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>회복 포션</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>작은 회복 포션</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨라 알약</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>일시적으로 이동속도가 증가한다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력을 50을 회복시켜준다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력을 25을 회복 시켜준다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_BluePill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_BluePill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_RedPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_RedVial</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_RedPotion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_RedVial</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3DObject/BluePill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3DObject/RedPotin</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3DObject/RedVial</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PurchasePrice</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -247,7 +270,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -277,6 +300,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -460,7 +484,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -469,7 +493,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -697,190 +721,207 @@
     <col min="1" max="1" width="19.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="50.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.5546875" style="2" customWidth="1"/>
-    <col min="5" max="7" width="12.5546875" style="2"/>
-    <col min="8" max="8" width="28.44140625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="12.5546875" style="2"/>
+    <col min="4" max="4" width="15.109375" style="2" customWidth="1"/>
+    <col min="5" max="6" width="12.5546875" style="2"/>
+    <col min="7" max="7" width="14.33203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.44140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="24.88671875" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="12.5546875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="13.8">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="12" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="16" t="s">
+      <c r="F3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="13" t="s">
-        <v>23</v>
+      <c r="J3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="4">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="E4" s="4">
+        <v>50</v>
       </c>
       <c r="G4" s="4">
-        <v>100</v>
-      </c>
-      <c r="H4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="4">
+        <v>25</v>
+      </c>
+      <c r="I4" s="4">
+        <v>50</v>
+      </c>
+      <c r="J4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="K4" s="17" t="s">
+        <v>33</v>
+      </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1000</v>
+        <v>14</v>
+      </c>
+      <c r="E5" s="4">
+        <v>25</v>
       </c>
       <c r="G5" s="4">
-        <v>1000</v>
-      </c>
-      <c r="H5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="4">
+        <v>50</v>
+      </c>
+      <c r="I5" s="4">
+        <v>100</v>
+      </c>
+      <c r="J5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="K5" s="17" t="s">
+        <v>34</v>
+      </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="4">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="4">
+        <v>75</v>
+      </c>
+      <c r="I6" s="4">
+        <v>150</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="4">
-        <v>100</v>
-      </c>
-      <c r="G7" s="4">
-        <v>20</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>1</v>
-      </c>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -888,30 +929,14 @@
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A8" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="4">
-        <v>20</v>
-      </c>
-      <c r="G8" s="4">
-        <v>100</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="A8" s="15"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -2091,6 +2116,6 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\promotion_task_3D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE48054-6103-4380-B690-9D18673BA61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DE595C-6FC5-450F-AEF5-1807F8214852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7692" yWindow="1860" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6216" yWindow="1692" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -766,7 +766,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>0</v>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\promotion_task_3D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DE595C-6FC5-450F-AEF5-1807F8214852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180C290F-F917-416C-A793-68ECCA370B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6216" yWindow="1692" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1272" yWindow="2064" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -826,6 +826,9 @@
       <c r="E4" s="4">
         <v>50</v>
       </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
       <c r="G4" s="4">
         <v>10</v>
       </c>
@@ -860,6 +863,9 @@
       <c r="E5" s="4">
         <v>25</v>
       </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
       <c r="G5" s="4">
         <v>10</v>
       </c>
@@ -891,7 +897,9 @@
       <c r="D6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
       <c r="F6" s="2">
         <v>0.5</v>
       </c>
